--- a/stories/arbres/ATOM-SOC.CUI.001-05.xlsx
+++ b/stories/arbres/ATOM-SOC.CUI.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>C'est le soir. Idriss entre dans la cuisine. Papa est là. Idriss dit : je veux aider. Papa sourit. Papa dit : tu fais une tâche sûre, avec un adulte. Idriss ouvre l'eau. Il lave une feuille de salade. L'eau est froide. La feuille est lisse. Idriss pose la salade. Ensuite, il prend une cuillère. Il pose la cuillère près de l'assiette. Puis Idriss va au pain. Il apporte le pain à table. Papa dit : merci. Laver. Poser. Apporter. Ce sont des tâches sûres. Idriss reste avec papa.</t>
+          <t>C'est le soir. Idriss entre dans la cuisine. Papa est là. Je veux aider. Papa sourit. Tu fais une tâche sûre, avec un adulte. Idriss ouvre l'eau. Il lave une feuille de salade. L'eau est froide. La feuille est lisse. Idriss pose la salade. Ensuite, il prend une cuillère. Il pose la cuillère près de l'assiette. Puis Idriss va au pain. Il apporte le pain à table. Merci. Laver. Poser. Apporter. Ce sont des tâches sûres. Idriss reste avec papa.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,16 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Idriss entre dans la cuisine. Papa est là.
+enfant-m|Je veux aider. Papa sourit.
+papa|Tu fais une tâche sûre, avec un adulte.
+narrateur|Idriss ouvre l'eau. Il lave une feuille de salade. L'eau est froide. La feuille est lisse. Idriss pose la salade. Ensuite, il prend une cuillère. Il pose la cuillère près de l'assiette. Puis Idriss va au pain. Il apporte le pain à table.
+papa|Merci. Laver. Poser. Apporter. Ce sont des tâches sûres.
+narrateur|Idriss reste avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1491,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Idriss aide papa. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1664,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Idriss a lavé la salade. Il a posé la cuillère. Il a apporté le pain. Avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1827,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Idriss s'assoit. Il croque un morceau de pain. Papa est près de lui.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1994,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2034,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.CUI.001-05.xlsx
+++ b/stories/arbres/ATOM-SOC.CUI.001-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1315,6 +1320,7 @@
 narrateur|Idriss reste avec papa.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1498,6 +1504,7 @@
           <t>narrateur|Idriss aide papa. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1669,6 +1676,7 @@
           <t>narrateur|Idriss a lavé la salade. Il a posé la cuillère. Il a apporté le pain. Avec papa.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1832,6 +1840,7 @@
           <t>narrateur|Idriss s'assoit. Il croque un morceau de pain. Papa est près de lui.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1999,6 +2008,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2017,7 +2027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2041,6 +2051,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2242,6 +2266,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SOC.CUI.001-05.xlsx
+++ b/stories/arbres/ATOM-SOC.CUI.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Idriss aide papa à préparer</t>
+          <t>Le pain perdu de Raphaël</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Raphaël veut un pain perdu doré. L'œuf glisse. Papa le rattrape au-dessus du bol. Ils trempent le pain. Ça sent la cannelle.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>C'est le soir. Idriss entre dans la cuisine. Papa est là. Je veux aider. Papa sourit. Tu fais une tâche sûre, avec un adulte. Idriss ouvre l'eau. Il lave une feuille de salade. L'eau est froide. La feuille est lisse. Idriss pose la salade. Ensuite, il prend une cuillère. Il pose la cuillère près de l'assiette. Puis Idriss va au pain. Il apporte le pain à table. Merci. Laver. Poser. Apporter. Ce sont des tâches sûres. Idriss reste avec papa.</t>
+          <t>Le pain rassis attend dans le saladier. La pluie tape le carreau, tout doux. Une goutte fait un trait sur la vitre. Ça sent déjà un peu la cannelle. Tu as entendu la pluie, Raphaël ? Elle tape. Oui. On reste au chaud. En ce moment, Raphaël veut du pain perdu. Je veux le pain tout doré. On le fait ensemble ? Oui. Je peux aider ? Oui, avec moi. Papa pose un bol près du saladier. Raphaël tient l'œuf des deux mains. La coquille est froide et lisse. L'œuf glisse un peu. Il part ! Papa ouvre les mains au-dessus du bol. Il rattrape l'œuf, tout juste. On l'a. Il n'est pas par terre. Non. Il va dans le bol. Ils cassent l'œuf, cette fois ensemble. Le jaune tombe, tout rond. Raphaël bat avec la fourchette. Tu vois le mélange ? Il est jaune. Papa pose une tranche de pain. Raphaël la pousse dans le bol. Le pain boit le jaune, tout mou. Il est lourd. On le met dans la poêle ? Oui. Ça chuinte un peu. Un nuage sent la cannelle. Le pain dore sur un bord. Tu le tournes avec moi ? Oui. Ils le retournent, tout doux. L'autre face devient brune. Merci, Raphaël. Tu as aidé. Papa glisse le pain dans l'assiette. Raphaël l'apporte à table. La pluie chante encore. Il est chaud. On souffle ? Oui. Raphaël coupe un coin avec la fourchette. Le dedans est mou, le bord croque. Ça sent la cannelle. Oui. Une goutte descend encore la vitre. Raphaël regarde le trait d'eau. L'œuf a glissé. Et on l'a rattrapé. Au-dessus du bol. Oui. Le saladier n'a plus de pain rassis. L'assiette a un pain doré. C'est celui que je voulais. Oui. La poêle se tait. Le carreau reste tout mouillé.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;C'est le soir. Idriss entre dans la cuisine. Papa est là. Idriss dit : je veux aider. Papa sourit. Papa dit : tu fais une &lt;emphasis level="moderate"&gt;tâche&lt;/emphasis&gt; sûre, avec un adulte. Idriss ouvre l'eau. Il lave une feuille de salade. L'eau est froide. La feuille est lisse. Idriss pose la salade. Ensuite, il prend une cuillère. Il pose la cuillère près de l'assiette. Puis Idriss va au pain. Il apporte le pain à table. Papa dit : merci. Laver. Poser. Apporter. Ce sont des tâches sûres. Idriss reste avec papa.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le pain rassis attend dans le saladier. La pluie tape le carreau, tout doux. Une goutte fait un trait sur la vitre. Ça sent déjà un peu la cannelle. Tu as entendu la pluie, Raphaël ? Elle tape. Oui. On reste au chaud. En ce moment, Raphaël veut du pain perdu. Je veux le pain tout doré. On le fait ensemble ? Oui. Je peux aider ? Oui, avec moi. Papa pose un bol près du saladier. Raphaël tient l'œuf des deux mains. La coquille est froide et lisse. L'œuf glisse un peu. Il part ! Papa ouvre les mains au-dessus du bol. Il rattrape l'œuf, tout juste. On l'a. Il n'est pas par terre. Non. Il va dans le bol. Ils cassent l'œuf, cette fois ensemble. Le jaune tombe, tout rond. Raphaël bat avec la fourchette. Tu vois le mélange ? Il est jaune. Papa pose une tranche de pain. Raphaël la pousse dans le bol. Le pain boit le jaune, tout mou. Il est lourd. On le met dans la poêle ? Oui. Ça chuinte un peu. Un nuage sent la cannelle. Le pain dore sur un bord. Tu le tournes avec moi ? Oui. Ils le retournent, tout doux. L'autre face devient brune. Merci, Raphaël. Tu as aidé. Papa glisse le pain dans l'assiette. Raphaël l'apporte à table. La pluie chante encore. Il est chaud. On souffle ? Oui. Raphaël coupe un coin avec la fourchette. Le dedans est mou, le bord croque. Ça sent la cannelle. Oui. Une goutte descend encore la vitre. Raphaël regarde le trait d'eau. L'œuf a glissé. Et on l'a rattrapé. Au-dessus du bol. Oui. Le saladier n'a plus de pain rassis. L'assiette a un pain doré. C'est celui que je voulais. Oui. La poêle se tait. Le carreau reste tout mouillé.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,15 +1324,75 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|C'est le soir. Idriss entre dans la cuisine. Papa est là.
-enfant-m|Je veux aider. Papa sourit.
-papa|Tu fais une tâche sûre, avec un adulte.
-narrateur|Idriss ouvre l'eau. Il lave une feuille de salade. L'eau est froide. La feuille est lisse. Idriss pose la salade. Ensuite, il prend une cuillère. Il pose la cuillère près de l'assiette. Puis Idriss va au pain. Il apporte le pain à table.
-papa|Merci. Laver. Poser. Apporter. Ce sont des tâches sûres.
-narrateur|Idriss reste avec papa.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Le pain rassis attend dans le saladier.
+narrateur|La pluie tape le carreau, tout doux.
+narrateur|Une goutte fait un trait sur la vitre.
+narrateur|Ça sent déjà un peu la cannelle.
+papa|Tu as entendu la pluie, Raphaël ?
+enfant-m|Elle tape.
+papa|Oui.
+papa|On reste au chaud.
+narrateur|En ce moment, Raphaël veut du pain perdu.
+enfant-m|Je veux le pain tout doré.
+papa|On le fait ensemble ?
+enfant-m|Oui.
+enfant-m|Je peux aider ?
+papa|Oui, avec moi.
+narrateur|Papa pose un bol près du saladier.
+narrateur|Raphaël tient l'œuf des deux mains.
+narrateur|La coquille est froide et lisse.
+narrateur|L'œuf glisse un peu.
+enfant-m|Il part !
+narrateur|Papa ouvre les mains au-dessus du bol.
+narrateur|Il rattrape l'œuf, tout juste.
+papa|On l'a.
+enfant-m|Il n'est pas par terre.
+papa|Non.
+papa|Il va dans le bol.
+narrateur|Ils cassent l'œuf, cette fois ensemble.
+narrateur|Le jaune tombe, tout rond.
+narrateur|Raphaël bat avec la fourchette.
+papa|Tu vois le mélange ?
+enfant-m|Il est jaune.
+narrateur|Papa pose une tranche de pain.
+narrateur|Raphaël la pousse dans le bol.
+narrateur|Le pain boit le jaune, tout mou.
+enfant-m|Il est lourd.
+papa|On le met dans la poêle ?
+enfant-m|Oui.
+narrateur|Ça chuinte un peu.
+narrateur|Un nuage sent la cannelle.
+narrateur|Le pain dore sur un bord.
+papa|Tu le tournes avec moi ?
+enfant-m|Oui.
+narrateur|Ils le retournent, tout doux.
+narrateur|L'autre face devient brune.
+papa|Merci, Raphaël.
+papa|Tu as aidé.
+narrateur|Papa glisse le pain dans l'assiette.
+narrateur|Raphaël l'apporte à table.
+narrateur|La pluie chante encore.
+enfant-m|Il est chaud.
+papa|On souffle ?
+enfant-m|Oui.
+narrateur|Raphaël coupe un coin avec la fourchette.
+narrateur|Le dedans est mou, le bord croque.
+enfant-m|Ça sent la cannelle.
+papa|Oui.
+narrateur|Une goutte descend encore la vitre.
+narrateur|Raphaël regarde le trait d'eau.
+enfant-m|L'œuf a glissé.
+papa|Et on l'a rattrapé.
+enfant-m|Au-dessus du bol.
+papa|Oui.
+narrateur|Le saladier n'a plus de pain rassis.
+narrateur|L'assiette a un pain doré.
+enfant-m|C'est celui que je voulais.
+papa|Oui.
+narrateur|La poêle se tait.
+narrateur|Le carreau reste tout mouillé.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1345,12 +1417,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Idriss aide papa. Que fait-il ?</t>
+          <t>Raphaël prépare le pain perdu. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Idriss aide papa. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël prépare le pain perdu. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1365,7 +1437,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>aider | laver | apporter | avec papa</t>
+          <t>aider | le pain | tremper | avec papa | l'œuf | le bol</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1380,7 +1452,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Il lave la salade. Que fait Idriss ?</t>
+          <t>Raphaël aide papa. Que fait-il ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1429,7 +1501,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1501,10 +1573,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Idriss aide papa. Que fait-il ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Raphaël prépare le pain perdu.
+narrateur|Que fait-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1529,12 +1601,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Idriss a lavé la salade. Il a posé la cuillère. Il a apporté le pain. Avec papa.</t>
+          <t>L'œuf a glissé. Papa l'a rattrapé au-dessus du bol. Raphaël a trempé le pain. Tu as aidé, Raphaël. Il est doré. Oui. La cannelle sent encore. La pluie tape le carreau.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Idriss a lavé la salade. Il a posé la cuillère. Il a apporté le pain. &lt;emphasis level="moderate"&gt;avec&lt;/emphasis&gt; papa.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>L'œuf a glissé. Papa l'a rattrapé au-dessus du bol. Raphaël a trempé le pain. Tu as aidé, Raphaël. Il est doré. Oui. La cannelle sent encore. La pluie tape le carreau.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1597,7 +1669,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1673,10 +1745,16 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Idriss a lavé la salade. Il a posé la cuillère. Il a apporté le pain. Avec papa.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|L'œuf a glissé.
+narrateur|Papa l'a rattrapé au-dessus du bol.
+narrateur|Raphaël a trempé le pain.
+papa|Tu as aidé, Raphaël.
+enfant-m|Il est doré.
+papa|Oui.
+narrateur|La cannelle sent encore.
+narrateur|La pluie tape le carreau.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1701,12 +1779,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Idriss s'assoit. Il croque un morceau de pain. Papa est près de lui.</t>
+          <t>Raphaël pose sa fourchette. Il reste un coin ? Le plus doré. Il le mange, tout tiède. Merci pour le bol. L'œuf n'est pas tombé. Non. La vitre a encore des traits d'eau. La cuisine sent la cannelle.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Idriss s'assoit. Il croque un morceau de pain. Papa est près de lui.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël pose sa fourchette. Il reste un coin ? Le plus doré. Il le mange, tout tiède. Merci pour le bol. L'œuf n'est pas tombé. Non. La vitre a encore des traits d'eau. La cuisine sent la cannelle.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1769,7 +1847,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1837,10 +1915,17 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Idriss s'assoit. Il croque un morceau de pain. Papa est près de lui.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Raphaël pose sa fourchette.
+papa|Il reste un coin ?
+enfant-m|Le plus doré.
+narrateur|Il le mange, tout tiède.
+papa|Merci pour le bol.
+enfant-m|L'œuf n'est pas tombé.
+papa|Non.
+narrateur|La vitre a encore des traits d'eau.
+narrateur|La cuisine sent la cannelle.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1865,12 +1950,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël écoute encore la pluie. Le pain était doré. Oui. Un peu de cannelle reste au bord. Le pain perdu sent encore le chaud.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël écoute encore la pluie. Le pain était doré. Oui. Un peu de cannelle reste au bord. Le pain perdu sent encore le chaud.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1926,14 +2011,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2005,10 +2090,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Raphaël écoute encore la pluie.
+enfant-m|Le pain était doré.
+papa|Oui.
+narrateur|Un peu de cannelle reste au bord.
+narrateur|Le pain perdu sent encore le chaud.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2027,7 +2115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2065,6 +2153,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.CUI.001-05.xlsx
+++ b/stories/arbres/ATOM-SOC.CUI.001-05.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>cuisine</t>
+          <t>cuisine un soir de pluie, bol et poêle</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Idriss, papa</t>
+          <t>Raphaël, papa</t>
         </is>
       </c>
     </row>
